--- a/Deliverables/BOM/JLCPCB_BOM_John_Main.xlsx
+++ b/Deliverables/BOM/JLCPCB_BOM_John_Main.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\JohnWollam-MatrixProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="161">
   <si>
     <t>Comment</t>
   </si>
@@ -499,6 +499,9 @@
   </si>
   <si>
     <t>C60474</t>
+  </si>
+  <si>
+    <t>C2982040</t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1289,9 @@
       <c r="C24" s="7">
         <v>22232111</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="6" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
